--- a/AAAGameData/DataTables/AffixTable.xlsx
+++ b/AAAGameData/DataTables/AffixTable.xlsx
@@ -164,7 +164,7 @@
     <t>冷却缩减加成</t>
   </si>
   <si>
-    <t>冷却缩减+{0}</t>
+    <t>冷却缩减+{0}%</t>
   </si>
   <si>
     <t>初始法力加成</t>
@@ -1604,13 +1604,13 @@
         <v>10</v>
       </c>
       <c r="H15" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I15" s="1">
-        <v>0.3</v>
+        <v>5</v>
       </c>
       <c r="J15" s="1">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="K15" s="1">
         <v>7</v>
